--- a/output/pdf_financials_xlsx/NERD.xlsx
+++ b/output/pdf_financials_xlsx/NERD.xlsx
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.543171</v>
+        <v>0.044927</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.649824</v>
+        <v>0.046363</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.714481</v>
+        <v>0.069392</v>
       </c>
     </row>
     <row r="49">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/output/pdf_financials_xlsx/NERD.xlsx
+++ b/output/pdf_financials_xlsx/NERD.xlsx
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.044927</v>
+        <v>0.543171</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.046363</v>
+        <v>0.649824</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.069392</v>
+        <v>0.714481</v>
       </c>
     </row>
     <row r="49">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">

--- a/output/pdf_financials_xlsx/NERD.xlsx
+++ b/output/pdf_financials_xlsx/NERD.xlsx
@@ -969,16 +969,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.081305</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.062676</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.028075</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.001993</v>
       </c>
     </row>
     <row r="29">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.932829</v>
+        <v>-0.8515239999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.743552</v>
+        <v>-0.680876</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.443723</v>
+        <v>-0.415648</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.587357</v>
+        <v>-0.585364</v>
       </c>
     </row>
     <row r="30">
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-9.686753143449936</v>
+        <v>-8.842459640216013</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-7.064009606761214</v>
+        <v>-6.468565218052198</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-4.050700788773065</v>
+        <v>-3.794407054518128</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-4.860096103562544</v>
+        <v>-4.843604989071017</v>
       </c>
     </row>
     <row r="31">
@@ -2447,16 +2447,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.081305</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.062676</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.028075</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.001993</v>
       </c>
     </row>
     <row r="101">
@@ -2681,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.092321</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.043749</v>
       </c>
     </row>
     <row r="113">
@@ -4576,7 +4576,11 @@
           <t>Depreciation on property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.081305</v>
       </c>
@@ -4930,7 +4934,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -5754,18 +5762,22 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
-        <v>-0.081305</v>
+        <v>0.081305</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.062676</v>
+        <v>0.062676</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.028075</v>
+        <v>0.028075</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>-0.001993</v>
+        <v>0.001993</v>
       </c>
     </row>
     <row r="77">

--- a/output/pdf_financials_xlsx/NERD.xlsx
+++ b/output/pdf_financials_xlsx/NERD.xlsx
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.5380200000000001</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.516909</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.694259</v>
       </c>
     </row>
     <row r="65">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.5241710000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.50088</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.481819</v>
       </c>
     </row>
     <row r="68">
@@ -2504,16 +2504,16 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.082484</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.002102</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001436</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.023029</v>
       </c>
     </row>
     <row r="104">
@@ -2561,16 +2561,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.011123</v>
+        <v>0.07136099999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.237099</v>
+        <v>0.239201</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.101739</v>
+        <v>0.100303</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.042046</v>
+        <v>-0.06507499999999999</v>
       </c>
     </row>
     <row r="107">
@@ -4804,7 +4804,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.082484</v>
       </c>
